--- a/mixs-templates/MigsOrg_plus_combinations/MigsOrgPlantAssociated.xlsx
+++ b/mixs-templates/MigsOrg_plus_combinations/MigsOrgPlantAssociated.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>estimated_size</t>
+          <t>estimated_genome_size</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
